--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 3.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 3.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D418C4FB-0184-438D-806D-E9144412CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mjKwJBiCnkiRjHvcINDcBGnO+Sz9A=="/>
@@ -168,7 +167,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -395,7 +394,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -412,6 +410,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -638,7 +639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD846944-9F66-45A4-98F5-E6DA3A1F22FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -662,15 +663,15 @@
       <c r="B1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -702,8 +703,14 @@
       <c r="J2" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
+      <c r="K2" s="28">
+        <f>SUM(F3:F12)</f>
+        <v>730000</v>
+      </c>
+      <c r="L2" s="28">
+        <f>SUM(H3:H12)</f>
+        <v>700000</v>
+      </c>
     </row>
     <row r="3" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -713,16 +720,37 @@
       <c r="C3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="29"/>
+      <c r="D3" s="28" t="str">
+        <f>HLOOKUP(LEFT(C3,2),$B$15:$E$16,2,FALSE)</f>
+        <v>Reguler</v>
+      </c>
+      <c r="E3" s="28" t="str">
+        <f>VLOOKUP(RIGHT(C3,1),$G$15:$K$18,2,FALSE)</f>
+        <v>Dewasa</v>
+      </c>
+      <c r="F3" s="28">
+        <f>INDEX($H$15:$K$18,MATCH(E3,$H$15:$H$18,0),MATCH(D3,$H$15:$K$15,0))</f>
+        <v>60000</v>
+      </c>
+      <c r="G3" s="24">
+        <f>IF(AND(D3="Exekutif",E3="Lansia"),F3*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="28">
+        <f>F3-G3</f>
+        <v>60000</v>
+      </c>
       <c r="J3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="28"/>
+      <c r="K3" s="29">
+        <f>AVERAGE(F3:F12)</f>
+        <v>73000</v>
+      </c>
+      <c r="L3" s="35">
+        <f>AVERAGE(H3:H12)</f>
+        <v>70000</v>
+      </c>
     </row>
     <row r="4" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -732,16 +760,31 @@
       <c r="C4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="29"/>
-      <c r="J4" s="31" t="s">
+      <c r="D4" s="28" t="str">
+        <f t="shared" ref="D4:D12" si="0">HLOOKUP(LEFT(C4,2),$B$15:$E$16,2,FALSE)</f>
+        <v>Exekutif</v>
+      </c>
+      <c r="E4" s="28" t="str">
+        <f t="shared" ref="E4:E12" si="1">VLOOKUP(RIGHT(C4,1),$G$15:$K$18,2,FALSE)</f>
+        <v>Dewasa</v>
+      </c>
+      <c r="F4" s="28">
+        <f t="shared" ref="F4:F12" si="2">INDEX($H$15:$K$18,MATCH(E4,$H$15:$H$18,0),MATCH(D4,$H$15:$K$15,0))</f>
+        <v>100000</v>
+      </c>
+      <c r="G4" s="24">
+        <f t="shared" ref="G4:G12" si="3">IF(AND(D4="Exekutif",E4="Lansia"),F4*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="28">
+        <f t="shared" ref="H4:H12" si="4">F4-G4</f>
+        <v>100000</v>
+      </c>
+      <c r="J4" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
     </row>
     <row r="5" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -751,11 +794,26 @@
       <c r="C5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="29"/>
+      <c r="D5" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Reguler</v>
+      </c>
+      <c r="E5" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Dewasa</v>
+      </c>
+      <c r="F5" s="28">
+        <f t="shared" si="2"/>
+        <v>60000</v>
+      </c>
+      <c r="G5" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="28">
+        <f t="shared" si="4"/>
+        <v>60000</v>
+      </c>
       <c r="J5" s="25" t="s">
         <v>17</v>
       </c>
@@ -774,14 +832,38 @@
       <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
+      <c r="D6" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Exekutif</v>
+      </c>
+      <c r="E6" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Lansia</v>
+      </c>
+      <c r="F6" s="28">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="G6" s="24">
+        <f t="shared" si="3"/>
+        <v>15000</v>
+      </c>
+      <c r="H6" s="28">
+        <f t="shared" si="4"/>
+        <v>135000</v>
+      </c>
+      <c r="J6" s="28">
+        <f>COUNTIF($D$3:$D$12,J5)</f>
+        <v>4</v>
+      </c>
+      <c r="K6" s="28">
+        <f t="shared" ref="K6:L6" si="5">COUNTIF($D$3:$D$12,K5)</f>
+        <v>2</v>
+      </c>
+      <c r="L6" s="28">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -791,16 +873,31 @@
       <c r="C7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="29"/>
-      <c r="J7" s="31" t="s">
+      <c r="D7" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Reguler</v>
+      </c>
+      <c r="E7" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Dewasa</v>
+      </c>
+      <c r="F7" s="28">
+        <f t="shared" si="2"/>
+        <v>60000</v>
+      </c>
+      <c r="G7" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="28">
+        <f t="shared" si="4"/>
+        <v>60000</v>
+      </c>
+      <c r="J7" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
     </row>
     <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
@@ -810,11 +907,26 @@
       <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="29"/>
+      <c r="D8" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E8" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Anak</v>
+      </c>
+      <c r="F8" s="28">
+        <f t="shared" si="2"/>
+        <v>20000</v>
+      </c>
+      <c r="G8" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="28">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
       <c r="J8" s="25" t="s">
         <v>22</v>
       </c>
@@ -833,14 +945,38 @@
       <c r="C9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
+      <c r="D9" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Exekutif</v>
+      </c>
+      <c r="E9" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Lansia</v>
+      </c>
+      <c r="F9" s="28">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="3"/>
+        <v>15000</v>
+      </c>
+      <c r="H9" s="28">
+        <f t="shared" si="4"/>
+        <v>135000</v>
+      </c>
+      <c r="J9" s="28">
+        <f>COUNTIF($E$3:$E$12,J8)</f>
+        <v>3</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:L9" si="6">COUNTIF($E$3:$E$12,K8)</f>
+        <v>5</v>
+      </c>
+      <c r="L9" s="28">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -850,11 +986,26 @@
       <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="29"/>
+      <c r="D10" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E10" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Dewasa</v>
+      </c>
+      <c r="F10" s="28">
+        <f t="shared" si="2"/>
+        <v>50000</v>
+      </c>
+      <c r="G10" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="28">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
     </row>
     <row r="11" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
@@ -864,11 +1015,26 @@
       <c r="C11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="29"/>
+      <c r="D11" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Exekutif</v>
+      </c>
+      <c r="E11" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Anak</v>
+      </c>
+      <c r="F11" s="28">
+        <f t="shared" si="2"/>
+        <v>50000</v>
+      </c>
+      <c r="G11" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="28">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
     </row>
     <row r="12" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -878,11 +1044,26 @@
       <c r="C12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="29"/>
+      <c r="D12" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Reguler</v>
+      </c>
+      <c r="E12" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Anak</v>
+      </c>
+      <c r="F12" s="28">
+        <f t="shared" si="2"/>
+        <v>30000</v>
+      </c>
+      <c r="G12" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="28">
+        <f t="shared" si="4"/>
+        <v>30000</v>
+      </c>
     </row>
     <row r="13" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
@@ -913,10 +1094,10 @@
     </row>
     <row r="14" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="33"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -2468,7 +2649,7 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" xr:uid="{9CB15DF0-B442-480C-907A-DB92F0AB1AFE}"/>
+    <hyperlink ref="E1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 3.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 3.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D418C4FB-0184-438D-806D-E9144412CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mjKwJBiCnkiRjHvcINDcBGnO+Sz9A=="/>
@@ -167,7 +168,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -394,6 +395,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -410,9 +412,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -639,7 +638,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD846944-9F66-45A4-98F5-E6DA3A1F22FA}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -663,15 +662,15 @@
       <c r="B1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -703,14 +702,8 @@
       <c r="J2" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="28">
-        <f>SUM(F3:F12)</f>
-        <v>730000</v>
-      </c>
-      <c r="L2" s="28">
-        <f>SUM(H3:H12)</f>
-        <v>700000</v>
-      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -720,37 +713,16 @@
       <c r="C3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="28" t="str">
-        <f>HLOOKUP(LEFT(C3,2),$B$15:$E$16,2,FALSE)</f>
-        <v>Reguler</v>
-      </c>
-      <c r="E3" s="28" t="str">
-        <f>VLOOKUP(RIGHT(C3,1),$G$15:$K$18,2,FALSE)</f>
-        <v>Dewasa</v>
-      </c>
-      <c r="F3" s="28">
-        <f>INDEX($H$15:$K$18,MATCH(E3,$H$15:$H$18,0),MATCH(D3,$H$15:$K$15,0))</f>
-        <v>60000</v>
-      </c>
-      <c r="G3" s="24">
-        <f>IF(AND(D3="Exekutif",E3="Lansia"),F3*0.1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="28">
-        <f>F3-G3</f>
-        <v>60000</v>
-      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="29"/>
       <c r="J3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="29">
-        <f>AVERAGE(F3:F12)</f>
-        <v>73000</v>
-      </c>
-      <c r="L3" s="35">
-        <f>AVERAGE(H3:H12)</f>
-        <v>70000</v>
-      </c>
+      <c r="K3" s="30"/>
+      <c r="L3" s="28"/>
     </row>
     <row r="4" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -760,31 +732,16 @@
       <c r="C4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="28" t="str">
-        <f t="shared" ref="D4:D12" si="0">HLOOKUP(LEFT(C4,2),$B$15:$E$16,2,FALSE)</f>
-        <v>Exekutif</v>
-      </c>
-      <c r="E4" s="28" t="str">
-        <f t="shared" ref="E4:E12" si="1">VLOOKUP(RIGHT(C4,1),$G$15:$K$18,2,FALSE)</f>
-        <v>Dewasa</v>
-      </c>
-      <c r="F4" s="28">
-        <f t="shared" ref="F4:F12" si="2">INDEX($H$15:$K$18,MATCH(E4,$H$15:$H$18,0),MATCH(D4,$H$15:$K$15,0))</f>
-        <v>100000</v>
-      </c>
-      <c r="G4" s="24">
-        <f t="shared" ref="G4:G12" si="3">IF(AND(D4="Exekutif",E4="Lansia"),F4*0.1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="28">
-        <f t="shared" ref="H4:H12" si="4">F4-G4</f>
-        <v>100000</v>
-      </c>
-      <c r="J4" s="30" t="s">
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="29"/>
+      <c r="J4" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -794,26 +751,11 @@
       <c r="C5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Reguler</v>
-      </c>
-      <c r="E5" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Dewasa</v>
-      </c>
-      <c r="F5" s="28">
-        <f t="shared" si="2"/>
-        <v>60000</v>
-      </c>
-      <c r="G5" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="28">
-        <f t="shared" si="4"/>
-        <v>60000</v>
-      </c>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="29"/>
       <c r="J5" s="25" t="s">
         <v>17</v>
       </c>
@@ -832,38 +774,14 @@
       <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Exekutif</v>
-      </c>
-      <c r="E6" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Lansia</v>
-      </c>
-      <c r="F6" s="28">
-        <f t="shared" si="2"/>
-        <v>150000</v>
-      </c>
-      <c r="G6" s="24">
-        <f t="shared" si="3"/>
-        <v>15000</v>
-      </c>
-      <c r="H6" s="28">
-        <f t="shared" si="4"/>
-        <v>135000</v>
-      </c>
-      <c r="J6" s="28">
-        <f>COUNTIF($D$3:$D$12,J5)</f>
-        <v>4</v>
-      </c>
-      <c r="K6" s="28">
-        <f t="shared" ref="K6:L6" si="5">COUNTIF($D$3:$D$12,K5)</f>
-        <v>2</v>
-      </c>
-      <c r="L6" s="28">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
     </row>
     <row r="7" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -873,31 +791,16 @@
       <c r="C7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Reguler</v>
-      </c>
-      <c r="E7" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Dewasa</v>
-      </c>
-      <c r="F7" s="28">
-        <f t="shared" si="2"/>
-        <v>60000</v>
-      </c>
-      <c r="G7" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="28">
-        <f t="shared" si="4"/>
-        <v>60000</v>
-      </c>
-      <c r="J7" s="30" t="s">
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="29"/>
+      <c r="J7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
@@ -907,26 +810,11 @@
       <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="E8" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Anak</v>
-      </c>
-      <c r="F8" s="28">
-        <f t="shared" si="2"/>
-        <v>20000</v>
-      </c>
-      <c r="G8" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="28">
-        <f t="shared" si="4"/>
-        <v>20000</v>
-      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="29"/>
       <c r="J8" s="25" t="s">
         <v>22</v>
       </c>
@@ -945,38 +833,14 @@
       <c r="C9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Exekutif</v>
-      </c>
-      <c r="E9" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Lansia</v>
-      </c>
-      <c r="F9" s="28">
-        <f t="shared" si="2"/>
-        <v>150000</v>
-      </c>
-      <c r="G9" s="24">
-        <f t="shared" si="3"/>
-        <v>15000</v>
-      </c>
-      <c r="H9" s="28">
-        <f t="shared" si="4"/>
-        <v>135000</v>
-      </c>
-      <c r="J9" s="28">
-        <f>COUNTIF($E$3:$E$12,J8)</f>
-        <v>3</v>
-      </c>
-      <c r="K9" s="28">
-        <f t="shared" ref="K9:L9" si="6">COUNTIF($E$3:$E$12,K8)</f>
-        <v>5</v>
-      </c>
-      <c r="L9" s="28">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
     </row>
     <row r="10" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -986,26 +850,11 @@
       <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="E10" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Dewasa</v>
-      </c>
-      <c r="F10" s="28">
-        <f t="shared" si="2"/>
-        <v>50000</v>
-      </c>
-      <c r="G10" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="28">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
@@ -1015,26 +864,11 @@
       <c r="C11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Exekutif</v>
-      </c>
-      <c r="E11" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Anak</v>
-      </c>
-      <c r="F11" s="28">
-        <f t="shared" si="2"/>
-        <v>50000</v>
-      </c>
-      <c r="G11" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="28">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -1044,26 +878,11 @@
       <c r="C12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>Reguler</v>
-      </c>
-      <c r="E12" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Anak</v>
-      </c>
-      <c r="F12" s="28">
-        <f t="shared" si="2"/>
-        <v>30000</v>
-      </c>
-      <c r="G12" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="28">
-        <f t="shared" si="4"/>
-        <v>30000</v>
-      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
@@ -1094,10 +913,10 @@
     </row>
     <row r="14" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="32"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -2649,7 +2468,7 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1"/>
+    <hyperlink ref="E1" r:id="rId1" xr:uid="{9CB15DF0-B442-480C-907A-DB92F0AB1AFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
